--- a/LAS_Lahan.xlsx
+++ b/LAS_Lahan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D03EF15D-8605-4222-BE4D-E6B1670DA91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8BB98B5-B079-4DE6-BF5B-E8CADA8F042D}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{D03EF15D-8605-4222-BE4D-E6B1670DA91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3014990D-9085-4025-872E-04915DF563AD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BEED62CF-6B6B-4A19-9E26-39E82E5ABA88}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{BEED62CF-6B6B-4A19-9E26-39E82E5ABA88}"/>
   </bookViews>
   <sheets>
     <sheet name="LAS_Lahan" sheetId="1" r:id="rId1"/>
@@ -920,14 +920,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECBE6CB-BE0D-4A54-9F85-C13181ADFB39}">
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1000,20 +1000,8 @@
       <c r="X1" s="4">
         <v>2045</v>
       </c>
-      <c r="Y1" s="4">
-        <v>2046</v>
-      </c>
-      <c r="Z1" s="4">
-        <v>2047</v>
-      </c>
-      <c r="AA1" s="4">
-        <v>2048</v>
-      </c>
-      <c r="AB1" s="4">
-        <v>2049</v>
-      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1021,85 +1009,73 @@
         <v>2</v>
       </c>
       <c r="C2" s="8">
-        <v>1463618</v>
+        <v>1464013</v>
       </c>
       <c r="D2" s="9">
-        <v>1457145.4047630806</v>
+        <v>1453203.1404310418</v>
       </c>
       <c r="E2" s="9">
-        <v>1450701.4334492758</v>
+        <v>1442473.0978199253</v>
       </c>
       <c r="F2" s="9">
-        <v>1444285.9594742795</v>
+        <v>1431822.2828207188</v>
       </c>
       <c r="G2" s="9">
-        <v>1437898.8568135833</v>
+        <v>1421250.1104390549</v>
       </c>
       <c r="H2" s="9">
-        <v>1431539.9999999998</v>
+        <v>1410755.9999999998</v>
       </c>
       <c r="I2" s="5">
-        <v>1425495.1651514436</v>
+        <v>1400299.7450325543</v>
       </c>
       <c r="J2" s="5">
-        <v>1419475.8552818233</v>
+        <v>1389920.9898368227</v>
       </c>
       <c r="K2" s="5">
-        <v>1413481.9626091127</v>
+        <v>1379619.1599992474</v>
       </c>
       <c r="L2" s="5">
-        <v>1407513.3798064068</v>
+        <v>1369393.6853637148</v>
       </c>
       <c r="M2" s="5">
-        <v>1401570.0000000002</v>
+        <v>1359243.9999999998</v>
       </c>
       <c r="N2" s="6">
-        <v>1395704.7149552668</v>
+        <v>1350404.7815995659</v>
       </c>
       <c r="O2" s="6">
-        <v>1389863.9749340829</v>
+        <v>1341623.0449919009</v>
       </c>
       <c r="P2" s="6">
-        <v>1384047.6772205229</v>
+        <v>1332898.4163705946</v>
       </c>
       <c r="Q2" s="6">
-        <v>1378255.7195285065</v>
+        <v>1324230.5243601149</v>
       </c>
       <c r="R2" s="6">
-        <v>1372488.0000000002</v>
+        <v>1315618.9999999998</v>
       </c>
       <c r="S2" s="7">
-        <v>1367675.1642902815</v>
+        <v>1310890.5502286574</v>
       </c>
       <c r="T2" s="7">
-        <v>1362879.2055132347</v>
+        <v>1306179.0949194198</v>
       </c>
       <c r="U2" s="7">
-        <v>1358100.0644873555</v>
+        <v>1301484.5729927039</v>
       </c>
       <c r="V2" s="7">
-        <v>1353337.6822386687</v>
+        <v>1296806.9235884512</v>
       </c>
       <c r="W2" s="7">
-        <v>1348592</v>
+        <v>1292146.0860653406</v>
       </c>
       <c r="X2" s="10">
-        <v>1343917.5066456213</v>
-      </c>
-      <c r="Y2" s="10">
-        <v>1339259.2160331542</v>
-      </c>
-      <c r="Z2" s="10">
-        <v>1334617.0720006095</v>
-      </c>
-      <c r="AA2" s="10">
-        <v>1329991.0185806667</v>
-      </c>
-      <c r="AB2" s="10">
-        <v>1325380.9999999998</v>
+        <v>1287502.0000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1107,85 +1083,73 @@
         <v>3</v>
       </c>
       <c r="C3" s="8">
-        <v>336061</v>
+        <v>346362</v>
       </c>
       <c r="D3" s="9">
-        <v>336516.56320452731</v>
+        <v>342932.55703368457</v>
       </c>
       <c r="E3" s="9">
-        <v>336972.74396906106</v>
+        <v>339537.07009909092</v>
       </c>
       <c r="F3" s="9">
-        <v>337429.54313076357</v>
+        <v>336175.20298649004</v>
       </c>
       <c r="G3" s="9">
-        <v>337886.96152793203</v>
+        <v>332846.62281507498</v>
       </c>
       <c r="H3" s="9">
-        <v>338345.00000000006</v>
+        <v>329551</v>
       </c>
       <c r="I3" s="5">
-        <v>338832.39377182769</v>
+        <v>329974.90803354402</v>
       </c>
       <c r="J3" s="5">
-        <v>339320.48964561883</v>
+        <v>330399.36134845845</v>
       </c>
       <c r="K3" s="5">
-        <v>339809.28863276745</v>
+        <v>330824.36064614961</v>
       </c>
       <c r="L3" s="5">
-        <v>340298.79174612457</v>
+        <v>331249.90662892611</v>
       </c>
       <c r="M3" s="5">
-        <v>340789.00000000017</v>
+        <v>331675.99999999983</v>
       </c>
       <c r="N3" s="6">
-        <v>342356.31710022356</v>
+        <v>333967.1276204157</v>
       </c>
       <c r="O3" s="6">
-        <v>343930.84242281533</v>
+        <v>336274.08172744192</v>
       </c>
       <c r="P3" s="6">
-        <v>345512.60911899264</v>
+        <v>338596.97164614475</v>
       </c>
       <c r="Q3" s="6">
-        <v>347101.65049243794</v>
+        <v>340935.90745677799</v>
       </c>
       <c r="R3" s="6">
-        <v>348698.00000000012</v>
+        <v>343291.00000000006</v>
       </c>
       <c r="S3" s="7">
-        <v>351115.05843557778</v>
+        <v>343414.38907252485</v>
       </c>
       <c r="T3" s="7">
-        <v>353548.87111546152</v>
+        <v>343537.82249477989</v>
       </c>
       <c r="U3" s="7">
-        <v>355999.55417449435</v>
+        <v>343661.30028270569</v>
       </c>
       <c r="V3" s="7">
-        <v>358467.22455252748</v>
+        <v>343784.82245224866</v>
       </c>
       <c r="W3" s="7">
-        <v>360952.00000000017</v>
+        <v>343908.38901936082</v>
       </c>
       <c r="X3" s="10">
-        <v>363597.14626864763</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>366261.67682878685</v>
-      </c>
-      <c r="Z3" s="10">
-        <v>368945.73373333988</v>
-      </c>
-      <c r="AA3" s="10">
-        <v>371649.46007622796</v>
-      </c>
-      <c r="AB3" s="10">
-        <v>374373.00000000029</v>
+        <v>344032.00000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1196,82 +1160,70 @@
         <v>691</v>
       </c>
       <c r="D4" s="9">
-        <v>691</v>
+        <v>704.09424257543083</v>
       </c>
       <c r="E4" s="9">
-        <v>691</v>
+        <v>717.43661711703282</v>
       </c>
       <c r="F4" s="9">
-        <v>691</v>
+        <v>731.03182565108045</v>
       </c>
       <c r="G4" s="9">
-        <v>691</v>
+        <v>744.88465930583493</v>
       </c>
       <c r="H4" s="9">
-        <v>691</v>
+        <v>758.99999999999955</v>
       </c>
       <c r="I4" s="5">
-        <v>691</v>
+        <v>744.88465930583527</v>
       </c>
       <c r="J4" s="5">
-        <v>691</v>
+        <v>731.03182565108068</v>
       </c>
       <c r="K4" s="5">
-        <v>691</v>
+        <v>717.43661711703294</v>
       </c>
       <c r="L4" s="5">
-        <v>691</v>
+        <v>704.09424257543083</v>
       </c>
       <c r="M4" s="5">
-        <v>691</v>
+        <v>690.99999999999989</v>
       </c>
       <c r="N4" s="6">
-        <v>703.72278668800629</v>
+        <v>700.15421920934364</v>
       </c>
       <c r="O4" s="6">
-        <v>716.67982706792066</v>
+        <v>709.42971154362613</v>
       </c>
       <c r="P4" s="6">
-        <v>729.87543425081844</v>
+        <v>718.82808360309332</v>
       </c>
       <c r="Q4" s="6">
-        <v>743.31400076136708</v>
+        <v>728.35096327188512</v>
       </c>
       <c r="R4" s="6">
-        <v>757.00000000000011</v>
+        <v>738.00000000000011</v>
       </c>
       <c r="S4" s="7">
-        <v>758.79150045352446</v>
+        <v>737.66628964946051</v>
       </c>
       <c r="T4" s="7">
-        <v>760.58724063475699</v>
+        <v>737.33273019675028</v>
       </c>
       <c r="U4" s="7">
-        <v>762.38723057734887</v>
+        <v>736.99932157363617</v>
       </c>
       <c r="V4" s="7">
-        <v>764.19148033869703</v>
+        <v>736.66606371191563</v>
       </c>
       <c r="W4" s="7">
-        <v>766</v>
+        <v>736.33295654341714</v>
       </c>
       <c r="X4" s="10">
-        <v>774.22160772273185</v>
-      </c>
-      <c r="Y4" s="10">
-        <v>782.53145935348778</v>
-      </c>
-      <c r="Z4" s="10">
-        <v>790.93050202907682</v>
-      </c>
-      <c r="AA4" s="10">
-        <v>799.41969305208772</v>
-      </c>
-      <c r="AB4" s="10">
-        <v>808.00000000000011</v>
+        <v>735.99999999999989</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:24">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1279,85 +1231,73 @@
         <v>5</v>
       </c>
       <c r="C5" s="8">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="D5" s="9">
-        <v>1667.7030345661135</v>
+        <v>1644.1941283356357</v>
       </c>
       <c r="E5" s="9">
-        <v>1697.9446956660706</v>
+        <v>1646.3911885830576</v>
       </c>
       <c r="F5" s="9">
-        <v>1728.7347506030171</v>
+        <v>1648.5911846600434</v>
       </c>
       <c r="G5" s="9">
-        <v>1760.0831437976465</v>
+        <v>1650.7941204896058</v>
       </c>
       <c r="H5" s="9">
-        <v>1792</v>
+        <v>1652.9999999999998</v>
       </c>
       <c r="I5" s="5">
-        <v>1792</v>
+        <v>1651.3968935764867</v>
       </c>
       <c r="J5" s="5">
-        <v>1792</v>
+        <v>1649.7953418717907</v>
       </c>
       <c r="K5" s="5">
-        <v>1792</v>
+        <v>1648.1953433781202</v>
       </c>
       <c r="L5" s="5">
-        <v>1792</v>
+        <v>1646.5968965891461</v>
       </c>
       <c r="M5" s="5">
-        <v>1792</v>
+        <v>1644.9999999999995</v>
       </c>
       <c r="N5" s="6">
-        <v>1778.6011244153315</v>
+        <v>1645.799223017814</v>
       </c>
       <c r="O5" s="6">
-        <v>1765.3024329081927</v>
+        <v>1646.5988343380186</v>
       </c>
       <c r="P5" s="6">
-        <v>1752.1031763971159</v>
+        <v>1647.3988341492702</v>
       </c>
       <c r="Q5" s="6">
-        <v>1739.0026114015536</v>
+        <v>1648.1992226403172</v>
       </c>
       <c r="R5" s="6">
-        <v>1726.0000000000005</v>
+        <v>1648.9999999999995</v>
       </c>
       <c r="S5" s="7">
-        <v>1724.1962338657252</v>
+        <v>1649.8322824533852</v>
       </c>
       <c r="T5" s="7">
-        <v>1722.3943527675262</v>
+        <v>1650.6649849759531</v>
       </c>
       <c r="U5" s="7">
-        <v>1720.5943547354357</v>
+        <v>1651.4981077797208</v>
       </c>
       <c r="V5" s="7">
-        <v>1718.7962378015445</v>
+        <v>1652.3316510768125</v>
       </c>
       <c r="W5" s="7">
-        <v>1717.0000000000002</v>
+        <v>1653.165615079459</v>
       </c>
       <c r="X5" s="10">
-        <v>1708.5165828061938</v>
-      </c>
-      <c r="Y5" s="10">
-        <v>1700.0750807942652</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>1691.6752868681313</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>1683.3169949549372</v>
-      </c>
-      <c r="AB5" s="10">
-        <v>1675</v>
+        <v>1653.9999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:24">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1365,85 +1305,73 @@
         <v>6</v>
       </c>
       <c r="C6" s="8">
-        <v>3747</v>
+        <v>3755</v>
       </c>
       <c r="D6" s="9">
-        <v>3747</v>
+        <v>3745.1484426692282</v>
       </c>
       <c r="E6" s="9">
-        <v>3747</v>
+        <v>3735.3227317250985</v>
       </c>
       <c r="F6" s="9">
-        <v>3747</v>
+        <v>3725.5227993574485</v>
       </c>
       <c r="G6" s="9">
-        <v>3747</v>
+        <v>3715.7485779340218</v>
       </c>
       <c r="H6" s="9">
-        <v>3747</v>
+        <v>3706.0000000000005</v>
       </c>
       <c r="I6" s="5">
-        <v>3747</v>
+        <v>3695.3388376238649</v>
       </c>
       <c r="J6" s="5">
-        <v>3747</v>
+        <v>3684.7083445362382</v>
       </c>
       <c r="K6" s="5">
-        <v>3747</v>
+        <v>3674.1084325098486</v>
       </c>
       <c r="L6" s="5">
-        <v>3747</v>
+        <v>3663.5390135712319</v>
       </c>
       <c r="M6" s="5">
-        <v>3747</v>
+        <v>3652.9999999999991</v>
       </c>
       <c r="N6" s="6">
-        <v>3747.3999146256856</v>
+        <v>3647.7851321917592</v>
       </c>
       <c r="O6" s="6">
-        <v>3747.7998719339726</v>
+        <v>3642.5777089075418</v>
       </c>
       <c r="P6" s="6">
-        <v>3748.1998719294165</v>
+        <v>3637.3777195198613</v>
       </c>
       <c r="Q6" s="6">
-        <v>3748.5999146165732</v>
+        <v>3632.185153416402</v>
       </c>
       <c r="R6" s="6">
-        <v>3748.9999999999995</v>
+        <v>3626.9999999999986</v>
       </c>
       <c r="S6" s="7">
-        <v>3749.3999146712163</v>
+        <v>3622.1504853126039</v>
       </c>
       <c r="T6" s="7">
-        <v>3749.7998720022738</v>
+        <v>3617.3074547147316</v>
       </c>
       <c r="U6" s="7">
-        <v>3750.1998719977228</v>
+        <v>3612.47089953677</v>
       </c>
       <c r="V6" s="7">
-        <v>3750.5999146621148</v>
+        <v>3607.6408111206974</v>
       </c>
       <c r="W6" s="7">
-        <v>3751.0000000000009</v>
+        <v>3602.8171808200691</v>
       </c>
       <c r="X6" s="10">
-        <v>3754.393853018094</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>3757.7907767475463</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>3761.1907739666949</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>3764.5938474563909</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>3768.0000000000018</v>
+        <v>3598</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:24">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1451,85 +1379,73 @@
         <v>7</v>
       </c>
       <c r="C7" s="8">
-        <v>2213</v>
+        <v>2489</v>
       </c>
       <c r="D7" s="9">
-        <v>2214.5976914040948</v>
+        <v>2501.2782633454444</v>
       </c>
       <c r="E7" s="9">
-        <v>2216.1965362730889</v>
+        <v>2513.6170954939344</v>
       </c>
       <c r="F7" s="9">
-        <v>2217.7965354397352</v>
+        <v>2526.0167952320162</v>
       </c>
       <c r="G7" s="9">
-        <v>2219.3976897373868</v>
+        <v>2538.4776628201539</v>
       </c>
       <c r="H7" s="9">
-        <v>2220.9999999999991</v>
+        <v>2550.9999999999991</v>
       </c>
       <c r="I7" s="5">
-        <v>2221</v>
+        <v>2561.3162244317805</v>
       </c>
       <c r="J7" s="5">
-        <v>2221</v>
+        <v>2571.6741675960293</v>
       </c>
       <c r="K7" s="5">
-        <v>2221</v>
+        <v>2582.0739982029809</v>
       </c>
       <c r="L7" s="5">
-        <v>2221</v>
+        <v>2592.5158856451317</v>
       </c>
       <c r="M7" s="5">
-        <v>2221</v>
+        <v>2603.0000000000009</v>
       </c>
       <c r="N7" s="6">
-        <v>2225.7793860969073</v>
+        <v>2609.170674151047</v>
       </c>
       <c r="O7" s="6">
-        <v>2230.569056989611</v>
+        <v>2615.3559765078098</v>
       </c>
       <c r="P7" s="6">
-        <v>2235.3690348100376</v>
+        <v>2621.5559417479262</v>
       </c>
       <c r="Q7" s="6">
-        <v>2240.1793417377407</v>
+        <v>2627.770604631241</v>
       </c>
       <c r="R7" s="6">
-        <v>2245.0000000000014</v>
+        <v>2634</v>
       </c>
       <c r="S7" s="7">
-        <v>2244.5998573847869</v>
+        <v>2639.6364273895138</v>
       </c>
       <c r="T7" s="7">
-        <v>2244.1997860898909</v>
+        <v>2645.2849160218966</v>
       </c>
       <c r="U7" s="7">
-        <v>2243.7997861026006</v>
+        <v>2650.9454917066851</v>
       </c>
       <c r="V7" s="7">
-        <v>2243.3998574102061</v>
+        <v>2656.6181803086452</v>
       </c>
       <c r="W7" s="7">
-        <v>2243</v>
+        <v>2662.3030077478902</v>
       </c>
       <c r="X7" s="10">
-        <v>2242.1994287243397</v>
-      </c>
-      <c r="Y7" s="10">
-        <v>2241.3991431884774</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>2240.599143290427</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>2239.7994289282392</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>2239</v>
+        <v>2667.9999999999991</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:24">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1537,85 +1453,73 @@
         <v>8</v>
       </c>
       <c r="C8" s="8">
-        <v>72512</v>
+        <v>61261</v>
       </c>
       <c r="D8" s="9">
-        <v>74742.138035740558</v>
+        <v>63769.908309656159</v>
       </c>
       <c r="E8" s="9">
-        <v>77040.864934820376</v>
+        <v>66381.567487013817</v>
       </c>
       <c r="F8" s="9">
-        <v>79410.29017750427</v>
+        <v>69100.185633569869</v>
       </c>
       <c r="G8" s="9">
-        <v>81852.588122038243</v>
+        <v>71930.143191148862</v>
       </c>
       <c r="H8" s="9">
-        <v>84370.000000000015</v>
+        <v>74876.000000000015</v>
       </c>
       <c r="I8" s="5">
-        <v>86040.154620681831</v>
+        <v>76068.787177312348</v>
       </c>
       <c r="J8" s="5">
-        <v>87743.370951177407</v>
+        <v>77280.575653443564</v>
       </c>
       <c r="K8" s="5">
-        <v>89480.303467810212</v>
+        <v>78511.668122255258</v>
       </c>
       <c r="L8" s="5">
-        <v>91251.619602654071</v>
+        <v>79762.372099572807</v>
       </c>
       <c r="M8" s="5">
-        <v>93057.999999999971</v>
+        <v>81033.000000000015</v>
       </c>
       <c r="N8" s="6">
-        <v>94747.341033318633</v>
+        <v>81476.909689369553</v>
       </c>
       <c r="O8" s="6">
-        <v>96467.349748371809</v>
+        <v>81923.251175813333</v>
       </c>
       <c r="P8" s="6">
-        <v>98218.582875082284</v>
+        <v>82372.037781043298</v>
       </c>
       <c r="Q8" s="6">
-        <v>100001.60725004502</v>
+        <v>82823.282899749509</v>
       </c>
       <c r="R8" s="6">
-        <v>101817.00000000004</v>
+        <v>83276.999999999956</v>
       </c>
       <c r="S8" s="7">
-        <v>102773.2679148848</v>
+        <v>83798.274277807242</v>
       </c>
       <c r="T8" s="7">
-        <v>103738.51712292337</v>
+        <v>84322.811483826401</v>
       </c>
       <c r="U8" s="7">
-        <v>104712.83197665485</v>
+        <v>84850.632042430923</v>
       </c>
       <c r="V8" s="7">
-        <v>105696.29762085962</v>
+        <v>85381.756505841069</v>
       </c>
       <c r="W8" s="7">
-        <v>106689.00000000006</v>
+        <v>85916.205554924207</v>
       </c>
       <c r="X8" s="10">
-        <v>108110.60664640584</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>109551.15587786824</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>111010.90010002247</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>112490.09508175141</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>113989.00000000012</v>
+        <v>86454.000000000058</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:24">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1623,85 +1527,73 @@
         <v>9</v>
       </c>
       <c r="C9" s="8">
-        <v>2803</v>
+        <v>2730</v>
       </c>
       <c r="D9" s="9">
-        <v>2837.5382924402306</v>
+        <v>2909.5710795917839</v>
       </c>
       <c r="E9" s="9">
-        <v>2872.502162349133</v>
+        <v>3100.9537975080216</v>
       </c>
       <c r="F9" s="9">
-        <v>2907.8968536507418</v>
+        <v>3304.9250873185556</v>
       </c>
       <c r="G9" s="9">
-        <v>2943.7276748842114</v>
+        <v>3522.3129869155387</v>
       </c>
       <c r="H9" s="9">
-        <v>2979.9999999999986</v>
+        <v>3754.0000000000018</v>
       </c>
       <c r="I9" s="5">
-        <v>3102.1646562492519</v>
+        <v>3949.2136743042765</v>
       </c>
       <c r="J9" s="5">
-        <v>3229.3374343899463</v>
+        <v>4154.5787547447753</v>
       </c>
       <c r="K9" s="5">
-        <v>3361.7236416332648</v>
+        <v>4370.6231297847899</v>
       </c>
       <c r="L9" s="5">
-        <v>3499.5370017289401</v>
+        <v>4597.9021388856281</v>
       </c>
       <c r="M9" s="5">
-        <v>3642.9999999999986</v>
+        <v>4837.0000000000009</v>
       </c>
       <c r="N9" s="6">
-        <v>3793.2793906965885</v>
+        <v>5025.8641271049937</v>
       </c>
       <c r="O9" s="6">
-        <v>3949.7580389468794</v>
+        <v>5222.10258923317</v>
       </c>
       <c r="P9" s="6">
-        <v>4112.6916737236816</v>
+        <v>5426.0033225737225</v>
       </c>
       <c r="Q9" s="6">
-        <v>4282.3465732158929</v>
+        <v>5637.865505990444</v>
       </c>
       <c r="R9" s="6">
-        <v>4459.0000000000018</v>
+        <v>5858.0000000000036</v>
       </c>
       <c r="S9" s="7">
-        <v>4644.5088275931312</v>
+        <v>6052.1793757664682</v>
       </c>
       <c r="T9" s="7">
-        <v>4837.7354226486932</v>
+        <v>6252.7953561715594</v>
       </c>
       <c r="U9" s="7">
-        <v>5039.0008692648225</v>
+        <v>6460.0613000187532</v>
       </c>
       <c r="V9" s="7">
-        <v>5248.6396096770422</v>
+        <v>6674.1976384705731</v>
       </c>
       <c r="W9" s="7">
-        <v>5466.9999999999982</v>
+        <v>6895.4321094811994</v>
       </c>
       <c r="X9" s="10">
-        <v>5645.1982946423977</v>
-      </c>
-      <c r="Y9" s="10">
-        <v>5829.2050092982336</v>
-      </c>
-      <c r="Z9" s="10">
-        <v>6019.2094709367693</v>
-      </c>
-      <c r="AA9" s="10">
-        <v>6215.4071776893416</v>
-      </c>
-      <c r="AB9" s="10">
-        <v>6418</v>
+        <v>7123.9999999999973</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:24">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1709,85 +1601,73 @@
         <v>10</v>
       </c>
       <c r="C10" s="8">
-        <v>38091</v>
+        <v>38119</v>
       </c>
       <c r="D10" s="9">
-        <v>38842.552152976707</v>
+        <v>40707.544711607588</v>
       </c>
       <c r="E10" s="9">
-        <v>39608.932759883319</v>
+        <v>43471.869578098347</v>
       </c>
       <c r="F10" s="9">
-        <v>40390.434392625961</v>
+        <v>46423.911292206307</v>
       </c>
       <c r="G10" s="9">
-        <v>41187.35539568292</v>
+        <v>49576.417130963368</v>
       </c>
       <c r="H10" s="9">
-        <v>42000.000000000015</v>
+        <v>52942.999999999993</v>
       </c>
       <c r="I10" s="5">
-        <v>42464.223860112688</v>
+        <v>55241.220519784241</v>
       </c>
       <c r="J10" s="5">
-        <v>42933.578762899138</v>
+        <v>57639.205268221136</v>
       </c>
       <c r="K10" s="5">
-        <v>43408.121421512602</v>
+        <v>60141.284944315841</v>
       </c>
       <c r="L10" s="5">
-        <v>43887.909175953915</v>
+        <v>62751.978239845332</v>
       </c>
       <c r="M10" s="5">
-        <v>44373.000000000022</v>
+        <v>65475.999999999971</v>
       </c>
       <c r="N10" s="6">
-        <v>45401.412252151036</v>
+        <v>67010.19848703203</v>
       </c>
       <c r="O10" s="6">
-        <v>46453.659533720289</v>
+        <v>68580.345489514162</v>
       </c>
       <c r="P10" s="6">
-        <v>47530.29425802856</v>
+        <v>70187.283333764673</v>
       </c>
       <c r="Q10" s="6">
-        <v>48631.881641421627</v>
+        <v>71831.874083039977</v>
       </c>
       <c r="R10" s="6">
-        <v>49758.999999999978</v>
+        <v>73515</v>
       </c>
       <c r="S10" s="7">
-        <v>49892.284057637575</v>
+        <v>73938.681812260998</v>
       </c>
       <c r="T10" s="7">
-        <v>50025.925128881136</v>
+        <v>74364.805388489083</v>
       </c>
       <c r="U10" s="7">
-        <v>50159.92417002446</v>
+        <v>74793.384801063803</v>
       </c>
       <c r="V10" s="7">
-        <v>50294.282139922849</v>
+        <v>75224.434203466692</v>
       </c>
       <c r="W10" s="7">
-        <v>50428.999999999978</v>
+        <v>75657.967830748647</v>
       </c>
       <c r="X10" s="10">
-        <v>50566.448697893087</v>
-      </c>
-      <c r="Y10" s="10">
-        <v>50704.272024364043</v>
-      </c>
-      <c r="Z10" s="10">
-        <v>50842.471000496167</v>
-      </c>
-      <c r="AA10" s="10">
-        <v>50981.046650155811</v>
-      </c>
-      <c r="AB10" s="10">
-        <v>51119.999999999978</v>
+        <v>76094.000000000029</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:24">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1798,82 +1678,70 @@
         <v>14970</v>
       </c>
       <c r="D11" s="9">
-        <v>15104.945080925021</v>
+        <v>15986.006377945947</v>
       </c>
       <c r="E11" s="9">
-        <v>15241.106606396859</v>
+        <v>17070.968598245057</v>
       </c>
       <c r="F11" s="9">
-        <v>15378.495541893659</v>
+        <v>18229.566659269236</v>
       </c>
       <c r="G11" s="9">
-        <v>15517.122951740414</v>
+        <v>19466.798188528308</v>
       </c>
       <c r="H11" s="9">
-        <v>15657.000000000007</v>
+        <v>20788.000000000007</v>
       </c>
       <c r="I11" s="5">
-        <v>15781.794718255886</v>
+        <v>21793.342414464878</v>
       </c>
       <c r="J11" s="5">
-        <v>15907.584117594006</v>
+        <v>22847.304867910036</v>
       </c>
       <c r="K11" s="5">
-        <v>16034.376126158031</v>
+        <v>23952.238706659304</v>
       </c>
       <c r="L11" s="5">
-        <v>16162.1787352832</v>
+        <v>25110.608992073579</v>
       </c>
       <c r="M11" s="5">
-        <v>16290.999999999998</v>
+        <v>26325.000000000011</v>
       </c>
       <c r="N11" s="6">
-        <v>16426.1392735626</v>
+        <v>27250.758338791868</v>
       </c>
       <c r="O11" s="6">
-        <v>16562.399572431139</v>
+        <v>28209.072366162756</v>
       </c>
       <c r="P11" s="6">
-        <v>16699.790195884081</v>
+        <v>29201.086952014928</v>
       </c>
       <c r="Q11" s="6">
-        <v>16838.320520340505</v>
+        <v>30227.987227327911</v>
       </c>
       <c r="R11" s="6">
-        <v>16978.000000000011</v>
+        <v>31291.000000000007</v>
       </c>
       <c r="S11" s="7">
-        <v>17180.510991248615</v>
+        <v>31865.78252304158</v>
       </c>
       <c r="T11" s="7">
-        <v>17385.4375026749</v>
+        <v>32451.12319215692</v>
       </c>
       <c r="U11" s="7">
-        <v>17592.808346234655</v>
+        <v>33047.215949305013</v>
       </c>
       <c r="V11" s="7">
-        <v>17802.652677548289</v>
+        <v>33654.258298953202</v>
       </c>
       <c r="W11" s="7">
-        <v>18014.999999999996</v>
+        <v>34272.451373516662</v>
       </c>
       <c r="X11" s="10">
-        <v>18127.974138607082</v>
-      </c>
-      <c r="Y11" s="10">
-        <v>18241.656751041199</v>
-      </c>
-      <c r="Z11" s="10">
-        <v>18356.05228022327</v>
-      </c>
-      <c r="AA11" s="10">
-        <v>18471.165196936279</v>
-      </c>
-      <c r="AB11" s="10">
-        <v>18587.000000000007</v>
+        <v>34901.999999999985</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:24">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1881,85 +1749,73 @@
         <v>12</v>
       </c>
       <c r="C12" s="8">
-        <v>12144</v>
+        <v>10981</v>
       </c>
       <c r="D12" s="9">
-        <v>12428.913769567391</v>
+        <v>11566.210955192761</v>
       </c>
       <c r="E12" s="9">
-        <v>12720.511980512341</v>
+        <v>12182.609585649852</v>
       </c>
       <c r="F12" s="9">
-        <v>13018.951458377536</v>
+        <v>12831.857977632242</v>
       </c>
       <c r="G12" s="9">
-        <v>13324.392708033434</v>
+        <v>13515.706795043043</v>
       </c>
       <c r="H12" s="9">
-        <v>13637.000000000007</v>
+        <v>14236.000000000005</v>
       </c>
       <c r="I12" s="5">
-        <v>13839.873365254078</v>
+        <v>14788.601296722525</v>
       </c>
       <c r="J12" s="5">
-        <v>14045.764813835098</v>
+        <v>15362.653014429836</v>
       </c>
       <c r="K12" s="5">
-        <v>14254.719244820655</v>
+        <v>15958.987797857211</v>
       </c>
       <c r="L12" s="5">
-        <v>14466.782225237817</v>
+        <v>16578.47061265595</v>
       </c>
       <c r="M12" s="5">
-        <v>14681.999999999998</v>
+        <v>17222.000000000004</v>
       </c>
       <c r="N12" s="6">
-        <v>14874.86594186253</v>
+        <v>17750.01487027415</v>
       </c>
       <c r="O12" s="6">
-        <v>15070.265412640094</v>
+        <v>18294.21831929819</v>
       </c>
       <c r="P12" s="6">
-        <v>15268.231693318961</v>
+        <v>18855.106677945922</v>
       </c>
       <c r="Q12" s="6">
-        <v>15468.798502071671</v>
+        <v>19433.191494259991</v>
       </c>
       <c r="R12" s="6">
-        <v>15672.000000000002</v>
+        <v>20029</v>
       </c>
       <c r="S12" s="7">
-        <v>15909.492219274956</v>
+        <v>20540.538044468525</v>
       </c>
       <c r="T12" s="7">
-        <v>16150.58337641465</v>
+        <v>21065.140703792444</v>
       </c>
       <c r="U12" s="7">
-        <v>16395.328009432131</v>
+        <v>21603.141646529093</v>
       </c>
       <c r="V12" s="7">
-        <v>16643.781482805083</v>
+        <v>22154.883063087185</v>
       </c>
       <c r="W12" s="7">
-        <v>16896.000000000004</v>
+        <v>22720.715883373792</v>
       </c>
       <c r="X12" s="10">
-        <v>16996.399695182237</v>
-      </c>
-      <c r="Y12" s="10">
-        <v>17097.395987120668</v>
-      </c>
-      <c r="Z12" s="10">
-        <v>17198.992420922565</v>
-      </c>
-      <c r="AA12" s="10">
-        <v>17301.192562761</v>
-      </c>
-      <c r="AB12" s="10">
-        <v>17404.000000000011</v>
+        <v>23300.999999999985</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:24">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1970,82 +1826,70 @@
         <v>74927</v>
       </c>
       <c r="D13" s="9">
-        <v>75263.169894126942</v>
+        <v>75409.934337249448</v>
       </c>
       <c r="E13" s="9">
-        <v>75600.848058940246</v>
+        <v>75895.981378518729</v>
       </c>
       <c r="F13" s="9">
-        <v>75940.041261495819</v>
+        <v>76385.161186424171</v>
       </c>
       <c r="G13" s="9">
-        <v>76280.756299210829</v>
+        <v>76877.493952893637</v>
       </c>
       <c r="H13" s="9">
-        <v>76622.999999999985</v>
+        <v>77373</v>
       </c>
       <c r="I13" s="5">
-        <v>76814.044952852128</v>
+        <v>77478.710750758997</v>
       </c>
       <c r="J13" s="5">
-        <v>77005.566240147047</v>
+        <v>77584.565928680255</v>
       </c>
       <c r="K13" s="5">
-        <v>77197.565049534576</v>
+        <v>77690.565731087176</v>
       </c>
       <c r="L13" s="5">
-        <v>77390.042571625687</v>
+        <v>77796.710355572766</v>
       </c>
       <c r="M13" s="5">
-        <v>77582.999999999942</v>
+        <v>77902.999999999985</v>
       </c>
       <c r="N13" s="6">
-        <v>77665.225523474932</v>
+        <v>78193.229415781723</v>
       </c>
       <c r="O13" s="6">
-        <v>77747.538192802822</v>
+        <v>78484.540087917951</v>
       </c>
       <c r="P13" s="6">
-        <v>77829.938100344298</v>
+        <v>78776.936044654067</v>
       </c>
       <c r="Q13" s="6">
-        <v>77912.425338557849</v>
+        <v>79070.421329242774</v>
       </c>
       <c r="R13" s="6">
-        <v>77994.999999999971</v>
+        <v>79365.000000000015</v>
       </c>
       <c r="S13" s="7">
-        <v>78270.250372148425</v>
+        <v>79768.665590469638</v>
       </c>
       <c r="T13" s="7">
-        <v>78546.472124095148</v>
+        <v>80174.384301444894</v>
       </c>
       <c r="U13" s="7">
-        <v>78823.668683914409</v>
+        <v>80582.1665754899</v>
       </c>
       <c r="V13" s="7">
-        <v>79101.843491778403</v>
+        <v>80992.022908281651</v>
       </c>
       <c r="W13" s="7">
-        <v>79380.999999999942</v>
+        <v>81403.963848880172</v>
       </c>
       <c r="X13" s="10">
-        <v>79666.341249808</v>
-      </c>
-      <c r="Y13" s="10">
-        <v>79952.708181187743</v>
-      </c>
-      <c r="Z13" s="10">
-        <v>80240.104481032278</v>
-      </c>
-      <c r="AA13" s="10">
-        <v>80528.533849487532</v>
-      </c>
-      <c r="AB13" s="10">
-        <v>80817.999999999913</v>
+        <v>81818.000000000015</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:24">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2053,85 +1897,73 @@
         <v>14</v>
       </c>
       <c r="C14" s="8">
-        <v>84707</v>
+        <v>81450</v>
       </c>
       <c r="D14" s="9">
-        <v>86112.198672273516</v>
+        <v>81262.135376130711</v>
       </c>
       <c r="E14" s="9">
-        <v>87540.708089922962</v>
+        <v>81074.704062475066</v>
       </c>
       <c r="F14" s="9">
-        <v>88992.914953320826</v>
+        <v>80887.705059601998</v>
       </c>
       <c r="G14" s="9">
-        <v>90469.212377785821</v>
+        <v>80701.137370385637</v>
       </c>
       <c r="H14" s="9">
-        <v>91969.999999999985</v>
+        <v>80514.999999999985</v>
       </c>
       <c r="I14" s="5">
-        <v>93341.670155936998</v>
+        <v>80134.419081943415</v>
       </c>
       <c r="J14" s="5">
-        <v>94733.797841684674</v>
+        <v>79755.637106135953</v>
       </c>
       <c r="K14" s="5">
-        <v>96146.688167421409</v>
+        <v>79378.64556927896</v>
       </c>
       <c r="L14" s="5">
-        <v>97580.650793836903</v>
+        <v>79003.43600826741</v>
       </c>
       <c r="M14" s="5">
-        <v>99035.999999999956</v>
+        <v>78629.999999999985</v>
       </c>
       <c r="N14" s="6">
-        <v>99650.916385427729</v>
+        <v>77885.016352049774</v>
       </c>
       <c r="O14" s="6">
-        <v>100269.65079825021</v>
+        <v>77147.091086850574</v>
       </c>
       <c r="P14" s="6">
-        <v>100892.2269446713</v>
+        <v>76416.157329421723</v>
       </c>
       <c r="Q14" s="6">
-        <v>101518.66867808714</v>
+        <v>75692.148838392706</v>
       </c>
       <c r="R14" s="6">
-        <v>102149.00000000001</v>
+        <v>74975.000000000015</v>
       </c>
       <c r="S14" s="7">
-        <v>102305.51960462687</v>
+        <v>74368.8811611977</v>
       </c>
       <c r="T14" s="7">
-        <v>102462.27903917505</v>
+        <v>73767.662356363406</v>
       </c>
       <c r="U14" s="7">
-        <v>102619.27867112817</v>
+        <v>73171.303972254042</v>
       </c>
       <c r="V14" s="7">
-        <v>102776.51886853293</v>
+        <v>72579.766715871068</v>
       </c>
       <c r="W14" s="7">
-        <v>102933.99999999999</v>
+        <v>71993.011611871523</v>
       </c>
       <c r="X14" s="10">
-        <v>103820.7882318617</v>
-      </c>
-      <c r="Y14" s="10">
-        <v>104715.21624618761</v>
-      </c>
-      <c r="Z14" s="10">
-        <v>105617.34986058106</v>
-      </c>
-      <c r="AA14" s="10">
-        <v>106527.25545967159</v>
-      </c>
-      <c r="AB14" s="10">
-        <v>107445</v>
+        <v>71410.999999999985</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:24">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2139,85 +1971,73 @@
         <v>15</v>
       </c>
       <c r="C15" s="8">
-        <v>9667</v>
+        <v>26547</v>
       </c>
       <c r="D15" s="9">
-        <v>9362.8545216068378</v>
+        <v>27307.55468995557</v>
       </c>
       <c r="E15" s="9">
-        <v>9068.2781413854991</v>
+        <v>28089.8987887488</v>
       </c>
       <c r="F15" s="9">
-        <v>8782.9697940684473</v>
+        <v>28894.656549104402</v>
       </c>
       <c r="G15" s="9">
-        <v>8506.6378865759852</v>
+        <v>29722.470108191184</v>
       </c>
       <c r="H15" s="9">
-        <v>8239</v>
+        <v>30574.000000000015</v>
       </c>
       <c r="I15" s="5">
-        <v>8040.0180163797841</v>
+        <v>31105.776936384176</v>
       </c>
       <c r="J15" s="5">
-        <v>7845.8416924033882</v>
+        <v>31646.803127366053</v>
       </c>
       <c r="K15" s="5">
-        <v>7656.354965479657</v>
+        <v>32197.239446245618</v>
       </c>
       <c r="L15" s="5">
-        <v>7471.4445760717635</v>
+        <v>32757.249564409816</v>
       </c>
       <c r="M15" s="5">
-        <v>7290.9999999999991</v>
+        <v>33326.999999999985</v>
       </c>
       <c r="N15" s="6">
-        <v>7183.4749461226675</v>
+        <v>33812.827608534251</v>
       </c>
       <c r="O15" s="6">
-        <v>7077.5356331877738</v>
+        <v>34305.737416642842</v>
       </c>
       <c r="P15" s="6">
-        <v>6973.1586752564535</v>
+        <v>34805.832665784124</v>
       </c>
       <c r="Q15" s="6">
-        <v>6870.3210312772817</v>
+        <v>35313.218102428924</v>
       </c>
       <c r="R15" s="6">
-        <v>6769</v>
+        <v>35828.000000000007</v>
       </c>
       <c r="S15" s="7">
-        <v>6767.5994205297638</v>
+        <v>36209.688768524233</v>
       </c>
       <c r="T15" s="7">
-        <v>6766.1991308546012</v>
+        <v>36595.443806893767</v>
       </c>
       <c r="U15" s="7">
-        <v>6764.7991309145509</v>
+        <v>36985.308434566286</v>
       </c>
       <c r="V15" s="7">
-        <v>6763.3994206496627</v>
+        <v>37379.326432497473</v>
       </c>
       <c r="W15" s="7">
-        <v>6762</v>
+        <v>37777.542048057519</v>
       </c>
       <c r="X15" s="10">
-        <v>6721.518191254655</v>
-      </c>
-      <c r="Y15" s="10">
-        <v>6681.2787334172217</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>6641.2801756147173</v>
-      </c>
-      <c r="AA15" s="10">
-        <v>6601.5210756600463</v>
-      </c>
-      <c r="AB15" s="10">
-        <v>6562</v>
+        <v>38180.000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:24">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2225,85 +2045,73 @@
         <v>16</v>
       </c>
       <c r="C16" s="8">
-        <v>14158</v>
+        <v>7675</v>
       </c>
       <c r="D16" s="9">
-        <v>14094.431724406406</v>
+        <v>8002.4426283710745</v>
       </c>
       <c r="E16" s="9">
-        <v>14031.148865231935</v>
+        <v>8343.8551166606576</v>
       </c>
       <c r="F16" s="9">
-        <v>13968.150140979937</v>
+        <v>8699.8334684713154</v>
       </c>
       <c r="G16" s="9">
-        <v>13905.434275907573</v>
+        <v>9070.9991150259593</v>
       </c>
       <c r="H16" s="9">
-        <v>13842.999999999995</v>
+        <v>9458.0000000000036</v>
       </c>
       <c r="I16" s="5">
-        <v>13921.504527826948</v>
+        <v>9762.8979823960581</v>
       </c>
       <c r="J16" s="5">
-        <v>14000.454259792403</v>
+        <v>10077.624975118739</v>
       </c>
       <c r="K16" s="5">
-        <v>14079.851720677167</v>
+        <v>10402.497836427454</v>
       </c>
       <c r="L16" s="5">
-        <v>14159.699449580237</v>
+        <v>10737.843639155948</v>
       </c>
       <c r="M16" s="5">
-        <v>14240.000000000002</v>
+        <v>11083.999999999996</v>
       </c>
       <c r="N16" s="6">
-        <v>14379.057480669726</v>
+        <v>11292.599225544618</v>
       </c>
       <c r="O16" s="6">
-        <v>14519.472895533989</v>
+        <v>11505.124257377382</v>
       </c>
       <c r="P16" s="6">
-        <v>14661.259505190263</v>
+        <v>11721.648978586649</v>
       </c>
       <c r="Q16" s="6">
-        <v>14804.430699729366</v>
+        <v>11942.248662729471</v>
       </c>
       <c r="R16" s="6">
-        <v>14949.000000000005</v>
+        <v>12167.000000000007</v>
       </c>
       <c r="S16" s="7">
-        <v>15079.501522340912</v>
+        <v>12312.732500725369</v>
       </c>
       <c r="T16" s="7">
-        <v>15211.142294620502</v>
+        <v>12460.21053952649</v>
       </c>
       <c r="U16" s="7">
-        <v>15343.932262243234</v>
+        <v>12609.455023909641</v>
       </c>
       <c r="V16" s="7">
-        <v>15477.881457434789</v>
+        <v>12760.487111804638</v>
       </c>
       <c r="W16" s="7">
-        <v>15613.000000000005</v>
+        <v>12913.328214564326</v>
       </c>
       <c r="X16" s="10">
-        <v>15769.818018759146</v>
-      </c>
-      <c r="Y16" s="10">
-        <v>15928.211128212424</v>
-      </c>
-      <c r="Z16" s="10">
-        <v>16088.19514867637</v>
-      </c>
-      <c r="AA16" s="10">
-        <v>16249.786059367836</v>
-      </c>
-      <c r="AB16" s="10">
-        <v>16413</v>
+        <v>13068.000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2311,85 +2119,73 @@
         <v>17</v>
       </c>
       <c r="C17" s="8">
-        <v>33043</v>
+        <v>42274</v>
       </c>
       <c r="D17" s="9">
-        <v>32788.716302052642</v>
+        <v>43546.989736404605</v>
       </c>
       <c r="E17" s="9">
-        <v>32536.38945424122</v>
+        <v>44858.312795158439</v>
       </c>
       <c r="F17" s="9">
-        <v>32286.004397549033</v>
+        <v>46209.123501045367</v>
       </c>
       <c r="G17" s="9">
-        <v>32037.546188846631</v>
+        <v>47600.610938834165</v>
       </c>
       <c r="H17" s="9">
-        <v>31791</v>
+        <v>49034</v>
       </c>
       <c r="I17" s="5">
-        <v>31535.113758311523</v>
+        <v>49261.086861339827</v>
       </c>
       <c r="J17" s="5">
-        <v>31281.287148867566</v>
+        <v>49489.225410133113</v>
       </c>
       <c r="K17" s="5">
-        <v>31029.503593656918</v>
+        <v>49718.420516967679</v>
       </c>
       <c r="L17" s="5">
-        <v>30779.746648105036</v>
+        <v>49948.677074988067</v>
       </c>
       <c r="M17" s="5">
-        <v>30532.000000000004</v>
+        <v>50180.000000000007</v>
       </c>
       <c r="N17" s="6">
-        <v>30399.250652714167</v>
+        <v>50274.443824652284</v>
       </c>
       <c r="O17" s="6">
-        <v>30267.078483117471</v>
+        <v>50369.065402114749</v>
       </c>
       <c r="P17" s="6">
-        <v>30135.480981712946</v>
+        <v>50463.86506693613</v>
       </c>
       <c r="Q17" s="6">
-        <v>30004.455649914602</v>
+        <v>50558.843154294802</v>
       </c>
       <c r="R17" s="6">
-        <v>29873.999999999989</v>
+        <v>50653.999999999993</v>
       </c>
       <c r="S17" s="7">
-        <v>29903.143084400348</v>
+        <v>51080.264310482606</v>
       </c>
       <c r="T17" s="7">
-        <v>29932.314598852525</v>
+        <v>51510.115726867829</v>
       </c>
       <c r="U17" s="7">
-        <v>29961.514571090996</v>
+        <v>51943.584435423771</v>
       </c>
       <c r="V17" s="7">
-        <v>29990.743028877285</v>
+        <v>52380.700876442468</v>
       </c>
       <c r="W17" s="7">
-        <v>30019.999999999989</v>
+        <v>52821.495746377565</v>
       </c>
       <c r="X17" s="10">
-        <v>30155.766417687417</v>
-      </c>
-      <c r="Y17" s="10">
-        <v>30292.146843375234</v>
-      </c>
-      <c r="Z17" s="10">
-        <v>30429.144053934415</v>
-      </c>
-      <c r="AA17" s="10">
-        <v>30566.76083879442</v>
-      </c>
-      <c r="AB17" s="10">
-        <v>30705</v>
+        <v>53265.999999999978</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2397,85 +2193,73 @@
         <v>18</v>
       </c>
       <c r="C18" s="8">
-        <v>46515</v>
+        <v>25656</v>
       </c>
       <c r="D18" s="9">
-        <v>46823.481164499353</v>
+        <v>26486.115802362001</v>
       </c>
       <c r="E18" s="9">
-        <v>47134.008134198128</v>
+        <v>27343.090516687331</v>
       </c>
       <c r="F18" s="9">
-        <v>47446.594476598635</v>
+        <v>28227.79317974146</v>
       </c>
       <c r="G18" s="9">
-        <v>47761.253849181026</v>
+        <v>29141.120946513744</v>
       </c>
       <c r="H18" s="9">
-        <v>48078</v>
+        <v>30084</v>
       </c>
       <c r="I18" s="5">
-        <v>48381.347829014609</v>
+        <v>30535.634608373053</v>
       </c>
       <c r="J18" s="5">
-        <v>48686.609629187915</v>
+        <v>30994.049359661953</v>
       </c>
       <c r="K18" s="5">
-        <v>48993.797476708525</v>
+        <v>31459.346040437315</v>
       </c>
       <c r="L18" s="5">
-        <v>49302.923523959675</v>
+        <v>31931.627965335774</v>
       </c>
       <c r="M18" s="5">
-        <v>49613.999999999993</v>
+        <v>32410.999999999996</v>
       </c>
       <c r="N18" s="6">
-        <v>48790.08604637596</v>
+        <v>32858.09379201047</v>
       </c>
       <c r="O18" s="6">
-        <v>47979.854404256264</v>
+        <v>33311.355022818083</v>
       </c>
       <c r="P18" s="6">
-        <v>47183.077858593417</v>
+        <v>33770.868769205379</v>
       </c>
       <c r="Q18" s="6">
-        <v>46399.532967582323</v>
+        <v>34236.721281547238</v>
       </c>
       <c r="R18" s="6">
-        <v>45628.999999999993</v>
+        <v>34709</v>
       </c>
       <c r="S18" s="7">
-        <v>44505.189351076951</v>
+        <v>35072.989390759503</v>
       </c>
       <c r="T18" s="7">
-        <v>43409.057379631668</v>
+        <v>35440.795897442411</v>
       </c>
       <c r="U18" s="7">
-        <v>42339.922379019306</v>
+        <v>35812.459549715364</v>
       </c>
       <c r="V18" s="7">
-        <v>41297.119432557251</v>
+        <v>36188.020797031633</v>
       </c>
       <c r="W18" s="7">
-        <v>40280</v>
+        <v>36567.520513033356</v>
       </c>
       <c r="X18" s="10">
-        <v>39402.599580157585</v>
-      </c>
-      <c r="Y18" s="10">
-        <v>38544.311163709892</v>
-      </c>
-      <c r="Z18" s="10">
-        <v>37704.718442816746</v>
-      </c>
-      <c r="AA18" s="10">
-        <v>36883.41417787713</v>
-      </c>
-      <c r="AB18" s="10">
-        <v>36079.999999999993</v>
+        <v>36950.999999999985</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2483,85 +2267,73 @@
         <v>19</v>
       </c>
       <c r="C19" s="8">
-        <v>17568</v>
+        <v>25109</v>
       </c>
       <c r="D19" s="9">
-        <v>16893.333437394744</v>
+        <v>25528.730728801002</v>
       </c>
       <c r="E19" s="9">
-        <v>16244.576196892036</v>
+        <v>25955.477821642777</v>
       </c>
       <c r="F19" s="9">
-        <v>15620.733278874257</v>
+        <v>26389.35856649348</v>
       </c>
       <c r="G19" s="9">
-        <v>15020.847894844677</v>
+        <v>26830.492211947509</v>
       </c>
       <c r="H19" s="9">
-        <v>14444.000000000002</v>
+        <v>27279.000000000011</v>
       </c>
       <c r="I19" s="5">
-        <v>14351.831203024396</v>
+        <v>27884.698450454754</v>
       </c>
       <c r="J19" s="5">
-        <v>14260.250545562496</v>
+        <v>28503.84573015117</v>
       </c>
       <c r="K19" s="5">
-        <v>14169.254274629569</v>
+        <v>29136.740454692168</v>
       </c>
       <c r="L19" s="5">
-        <v>14078.838661189107</v>
+        <v>29783.687870092635</v>
       </c>
       <c r="M19" s="5">
-        <v>13989.000000000004</v>
+        <v>30445.000000000007</v>
       </c>
       <c r="N19" s="6">
-        <v>13892.682771619842</v>
+        <v>30529.331513814872</v>
       </c>
       <c r="O19" s="6">
-        <v>13797.028707760583</v>
+        <v>30613.896622775821</v>
       </c>
       <c r="P19" s="6">
-        <v>13702.033242394011</v>
+        <v>30698.695973932685</v>
       </c>
       <c r="Q19" s="6">
-        <v>13607.691840929991</v>
+        <v>30783.730216127602</v>
       </c>
       <c r="R19" s="6">
-        <v>13513.999999999998</v>
+        <v>30868.999999999985</v>
       </c>
       <c r="S19" s="7">
-        <v>13241.640860984575</v>
+        <v>30714.923474128034</v>
       </c>
       <c r="T19" s="7">
-        <v>12974.770807406861</v>
+        <v>30561.615990849761</v>
       </c>
       <c r="U19" s="7">
-        <v>12713.2792130582</v>
+        <v>30409.07371164074</v>
       </c>
       <c r="V19" s="7">
-        <v>12457.057681274033</v>
+        <v>30257.292817135763</v>
       </c>
       <c r="W19" s="7">
-        <v>12206</v>
+        <v>30106.26950703323</v>
       </c>
       <c r="X19" s="10">
-        <v>11712.94313046935</v>
-      </c>
-      <c r="Y19" s="10">
-        <v>11239.803111388592</v>
-      </c>
-      <c r="Z19" s="10">
-        <v>10785.775408927335</v>
-      </c>
-      <c r="AA19" s="10">
-        <v>10350.087988102629</v>
-      </c>
-      <c r="AB19" s="10">
-        <v>9932.0000000000018</v>
+        <v>29956</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2569,85 +2341,73 @@
         <v>20</v>
       </c>
       <c r="C20" s="8">
-        <v>15353</v>
+        <v>14833</v>
       </c>
       <c r="D20" s="9">
-        <v>15949.081899466524</v>
+        <v>15746.214625291999</v>
       </c>
       <c r="E20" s="9">
-        <v>16568.306743691184</v>
+        <v>16715.652600671452</v>
       </c>
       <c r="F20" s="9">
-        <v>17211.573060028284</v>
+        <v>17744.775396210684</v>
       </c>
       <c r="G20" s="9">
-        <v>17879.814261254658</v>
+        <v>18837.257592283037</v>
       </c>
       <c r="H20" s="9">
-        <v>18574.000000000007</v>
+        <v>19996.999999999993</v>
       </c>
       <c r="I20" s="5">
-        <v>19123.68740260859</v>
+        <v>21021.178064650496</v>
       </c>
       <c r="J20" s="5">
-        <v>19689.642504182753</v>
+        <v>22097.8110329421</v>
       </c>
       <c r="K20" s="5">
-        <v>20272.346738403485</v>
+        <v>23229.585465943601</v>
       </c>
       <c r="L20" s="5">
-        <v>20872.295786719071</v>
+        <v>24419.325521209059</v>
       </c>
       <c r="M20" s="5">
-        <v>21489.999999999989</v>
+        <v>25669.999999999993</v>
       </c>
       <c r="N20" s="6">
-        <v>21980.310111090643</v>
+        <v>26599.243717805766</v>
       </c>
       <c r="O20" s="6">
-        <v>22481.807006966661</v>
+        <v>27562.125685984785</v>
       </c>
       <c r="P20" s="6">
-        <v>22994.745922327489</v>
+        <v>28559.863595726674</v>
       </c>
       <c r="Q20" s="6">
-        <v>23519.387915239426</v>
+        <v>29593.719218154354</v>
       </c>
       <c r="R20" s="6">
-        <v>24056.000000000011</v>
+        <v>30664.999999999996</v>
       </c>
       <c r="S20" s="7">
-        <v>25317.069230303143</v>
+        <v>31484.580216562372</v>
       </c>
       <c r="T20" s="7">
-        <v>26644.246525272785</v>
+        <v>32326.065267019425</v>
       </c>
       <c r="U20" s="7">
-        <v>28040.997417259521</v>
+        <v>33190.040599553358</v>
       </c>
       <c r="V20" s="7">
-        <v>29510.969109557318</v>
+        <v>34077.107309558116</v>
       </c>
       <c r="W20" s="7">
-        <v>31058.000000000004</v>
+        <v>34987.882557840741</v>
       </c>
       <c r="X20" s="10">
-        <v>31421.396040920783</v>
-      </c>
-      <c r="Y20" s="10">
-        <v>31789.044019588902</v>
-      </c>
-      <c r="Z20" s="10">
-        <v>32160.993686063724</v>
-      </c>
-      <c r="AA20" s="10">
-        <v>32537.295372508241</v>
-      </c>
-      <c r="AB20" s="10">
-        <v>32918.000000000015</v>
+        <v>35923.000000000007</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2655,85 +2415,73 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>40045</v>
+        <v>39002</v>
       </c>
       <c r="D21" s="9">
-        <v>40766.340296718277</v>
+        <v>39859.826114180221</v>
       </c>
       <c r="E21" s="9">
-        <v>41500.674271140881</v>
+        <v>40736.519610601601</v>
       </c>
       <c r="F21" s="9">
-        <v>42248.235981535523</v>
+        <v>41632.495466270251</v>
       </c>
       <c r="G21" s="9">
-        <v>43009.263702318261</v>
+        <v>42548.177785368149</v>
       </c>
       <c r="H21" s="9">
-        <v>43783.999999999993</v>
+        <v>43484</v>
       </c>
       <c r="I21" s="5">
-        <v>44519.847077839499</v>
+        <v>44446.625804511394</v>
       </c>
       <c r="J21" s="5">
-        <v>45268.061023072682</v>
+        <v>45430.561710198192</v>
       </c>
       <c r="K21" s="5">
-        <v>46028.849676993937</v>
+        <v>46436.279468814784</v>
       </c>
       <c r="L21" s="5">
-        <v>46802.424373940987</v>
+        <v>47464.261275506527</v>
       </c>
       <c r="M21" s="5">
-        <v>47589.000000000022</v>
+        <v>48514.999999999985</v>
       </c>
       <c r="N21" s="6">
-        <v>48224.593872202939</v>
+        <v>49027.26716831659</v>
       </c>
       <c r="O21" s="6">
-        <v>48868.676671897148</v>
+        <v>49544.943336978125</v>
       </c>
       <c r="P21" s="6">
-        <v>49521.361776339865</v>
+        <v>50068.085619316364</v>
       </c>
       <c r="Q21" s="6">
-        <v>50182.764077043525</v>
+        <v>50596.751731719531</v>
       </c>
       <c r="R21" s="6">
-        <v>50852.999999999978</v>
+        <v>51130.999999999971</v>
       </c>
       <c r="S21" s="7">
-        <v>50740.705149423266</v>
+        <v>51472.738752728685</v>
       </c>
       <c r="T21" s="7">
-        <v>50628.658271109052</v>
+        <v>51816.76154791921</v>
       </c>
       <c r="U21" s="7">
-        <v>50516.858817478889</v>
+        <v>52163.083651179964</v>
       </c>
       <c r="V21" s="7">
-        <v>50405.306242163475</v>
+        <v>52511.720430148423</v>
       </c>
       <c r="W21" s="7">
-        <v>50294.000000000015</v>
+        <v>52862.68735517309</v>
       </c>
       <c r="X21" s="10">
-        <v>49695.944966233757</v>
-      </c>
-      <c r="Y21" s="10">
-        <v>49105.001512843155</v>
-      </c>
-      <c r="Z21" s="10">
-        <v>48521.085074742077</v>
-      </c>
-      <c r="AA21" s="10">
-        <v>47944.112092423107</v>
-      </c>
-      <c r="AB21" s="10">
-        <v>47374.000000000007</v>
+        <v>53215.999999999971</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:24">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2741,85 +2489,73 @@
         <v>22</v>
       </c>
       <c r="C22" s="8">
-        <v>3918</v>
+        <v>3898</v>
       </c>
       <c r="D22" s="9">
-        <v>3962.5741755923982</v>
+        <v>4134.1898065760461</v>
       </c>
       <c r="E22" s="9">
-        <v>4007.6554612230152</v>
+        <v>4384.6909586447628</v>
       </c>
       <c r="F22" s="9">
-        <v>4053.2496261649212</v>
+        <v>4650.3706172948514</v>
       </c>
       <c r="G22" s="9">
-        <v>4099.3625053268652</v>
+        <v>4932.1484871270213</v>
       </c>
       <c r="H22" s="9">
-        <v>4145.9999999999973</v>
+        <v>5231</v>
       </c>
       <c r="I22" s="5">
-        <v>4182.7429512640356</v>
+        <v>5419.1669278024237</v>
       </c>
       <c r="J22" s="5">
-        <v>4219.8115283041425</v>
+        <v>5614.1025026548577</v>
       </c>
       <c r="K22" s="5">
-        <v>4257.2086169022841</v>
+        <v>5816.0502029592853</v>
       </c>
       <c r="L22" s="5">
-        <v>4294.9371284149893</v>
+        <v>6025.2622654015549</v>
       </c>
       <c r="M22" s="5">
-        <v>4332.9999999999991</v>
+        <v>6242.0000000000027</v>
       </c>
       <c r="N22" s="6">
-        <v>4365.8966817261198</v>
+        <v>6402.889497446683</v>
       </c>
       <c r="O22" s="6">
-        <v>4399.0431192031256</v>
+        <v>6567.9259718861003</v>
       </c>
       <c r="P22" s="6">
-        <v>4432.4412086081338</v>
+        <v>6737.2163129440578</v>
       </c>
       <c r="Q22" s="6">
-        <v>4466.0928605142772</v>
+        <v>6910.8701653598164</v>
       </c>
       <c r="R22" s="6">
-        <v>4499.9999999999991</v>
+        <v>7088.9999999999982</v>
       </c>
       <c r="S22" s="7">
-        <v>4718.6866751237521</v>
+        <v>7102.4361730771252</v>
       </c>
       <c r="T22" s="7">
-        <v>4948.000875108989</v>
+        <v>7115.8978124748819</v>
       </c>
       <c r="U22" s="7">
-        <v>5188.4590661949896</v>
+        <v>7129.3849664609934</v>
       </c>
       <c r="V22" s="7">
-        <v>5440.6028133509608</v>
+        <v>7142.8976833946681</v>
       </c>
       <c r="W22" s="7">
-        <v>5704.9999999999955</v>
+        <v>7156.4360117267724</v>
       </c>
       <c r="X22" s="10">
-        <v>5745.4230867661863</v>
-      </c>
-      <c r="Y22" s="10">
-        <v>5786.1325935049817</v>
-      </c>
-      <c r="Z22" s="10">
-        <v>5827.1305496606237</v>
-      </c>
-      <c r="AA22" s="10">
-        <v>5868.4189990570922</v>
-      </c>
-      <c r="AB22" s="10">
-        <v>5909.9999999999927</v>
+        <v>7170.0000000000027</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:24">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2830,82 +2566,70 @@
         <v>25332</v>
       </c>
       <c r="D23" s="9">
-        <v>25315.578723862094</v>
+        <v>25291.269230199789</v>
       </c>
       <c r="E23" s="9">
-        <v>25299.168092691423</v>
+        <v>25250.603950515182</v>
       </c>
       <c r="F23" s="9">
-        <v>25282.768099587469</v>
+        <v>25210.004055646055</v>
       </c>
       <c r="G23" s="9">
-        <v>25266.378737654184</v>
+        <v>25169.469440461588</v>
       </c>
       <c r="H23" s="9">
-        <v>25249.999999999996</v>
+        <v>25129</v>
       </c>
       <c r="I23" s="5">
-        <v>25233.779172572744</v>
+        <v>25088.670759723966</v>
       </c>
       <c r="J23" s="5">
-        <v>25217.568765551128</v>
+        <v>25048.406243377303</v>
       </c>
       <c r="K23" s="5">
-        <v>25201.368772240992</v>
+        <v>25008.206347085332</v>
       </c>
       <c r="L23" s="5">
-        <v>25185.179185952471</v>
+        <v>24968.070967140076</v>
       </c>
       <c r="M23" s="5">
-        <v>25169</v>
+        <v>24928.000000000004</v>
       </c>
       <c r="N23" s="6">
-        <v>25152.779105415226</v>
+        <v>24895.71648939537</v>
       </c>
       <c r="O23" s="6">
-        <v>25136.56866485807</v>
+        <v>24863.47478820413</v>
       </c>
       <c r="P23" s="6">
-        <v>25120.368671591132</v>
+        <v>24831.274842280152</v>
       </c>
       <c r="Q23" s="6">
-        <v>25104.179118881348</v>
+        <v>24799.116597547432</v>
       </c>
       <c r="R23" s="6">
-        <v>25088</v>
+        <v>24767</v>
       </c>
       <c r="S23" s="7">
-        <v>25072.380563220482</v>
+        <v>24760.662614019868</v>
       </c>
       <c r="T23" s="7">
-        <v>25056.770850883142</v>
+        <v>24754.326849651599</v>
       </c>
       <c r="U23" s="7">
-        <v>25041.170856933673</v>
+        <v>24747.992706480258</v>
       </c>
       <c r="V23" s="7">
-        <v>25025.58057532155</v>
+        <v>24741.660184091012</v>
       </c>
       <c r="W23" s="7">
-        <v>25010.000000000004</v>
+        <v>24735.329282069131</v>
       </c>
       <c r="X23" s="10">
-        <v>25008.399795242593</v>
-      </c>
-      <c r="Y23" s="10">
-        <v>25006.799692870438</v>
-      </c>
-      <c r="Z23" s="10">
-        <v>25005.199692876988</v>
-      </c>
-      <c r="AA23" s="10">
-        <v>25003.599795255694</v>
-      </c>
-      <c r="AB23" s="10">
-        <v>25002.000000000004</v>
+        <v>24729</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2916,82 +2640,70 @@
         <v>2737</v>
       </c>
       <c r="D24" s="9">
-        <v>2719.7847972276577</v>
+        <v>2587.2947148454482</v>
       </c>
       <c r="E24" s="9">
-        <v>2702.6778747645931</v>
+        <v>2445.7778375839198</v>
       </c>
       <c r="F24" s="9">
-        <v>2685.6785515485185</v>
+        <v>2312.0014880770932</v>
       </c>
       <c r="G24" s="9">
-        <v>2668.7861508008978</v>
+        <v>2185.5422838204877</v>
       </c>
       <c r="H24" s="9">
-        <v>2652.0000000000005</v>
+        <v>2065.9999999999995</v>
       </c>
       <c r="I24" s="5">
-        <v>2638.8706419727478</v>
+        <v>1993.4851341173764</v>
       </c>
       <c r="J24" s="5">
-        <v>2625.8062839614108</v>
+        <v>1923.5154791611685</v>
       </c>
       <c r="K24" s="5">
-        <v>2612.8066041679199</v>
+        <v>1856.001700364207</v>
       </c>
       <c r="L24" s="5">
-        <v>2599.8712823873429</v>
+        <v>1790.8575985346658</v>
       </c>
       <c r="M24" s="5">
-        <v>2586.9999999999995</v>
+        <v>1728.0000000000005</v>
       </c>
       <c r="N24" s="6">
-        <v>2578.7475171467386</v>
+        <v>1707.7299982654386</v>
       </c>
       <c r="O24" s="6">
-        <v>2570.5213595633818</v>
+        <v>1687.6977702405525</v>
       </c>
       <c r="P24" s="6">
-        <v>2562.3214432727982</v>
+        <v>1667.9005267624325</v>
       </c>
       <c r="Q24" s="6">
-        <v>2554.1476845657426</v>
+        <v>1648.3355113859566</v>
       </c>
       <c r="R24" s="6">
-        <v>2546</v>
+        <v>1629.0000000000002</v>
       </c>
       <c r="S24" s="7">
-        <v>2290.6717396390168</v>
+        <v>1620.8999738254149</v>
       </c>
       <c r="T24" s="7">
-        <v>2060.9493396625448</v>
+        <v>1612.840224154224</v>
       </c>
       <c r="U24" s="7">
-        <v>1854.2648897064746</v>
+        <v>1604.8205507158737</v>
       </c>
       <c r="V24" s="7">
-        <v>1668.3080049707303</v>
+        <v>1596.840754235634</v>
       </c>
       <c r="W24" s="7">
-        <v>1501</v>
+        <v>1588.900636429647</v>
       </c>
       <c r="X24" s="10">
-        <v>1476.4072270199736</v>
-      </c>
-      <c r="Y24" s="10">
-        <v>1452.2173884056015</v>
-      </c>
-      <c r="Z24" s="10">
-        <v>1428.4238823758176</v>
-      </c>
-      <c r="AA24" s="10">
-        <v>1405.0202153148473</v>
-      </c>
-      <c r="AB24" s="10">
-        <v>1382</v>
+        <v>1581</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:24">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2999,85 +2711,73 @@
         <v>25</v>
       </c>
       <c r="C25" s="8">
-        <v>3743</v>
+        <v>3747</v>
       </c>
       <c r="D25" s="9">
-        <v>3788.2906167923129</v>
+        <v>3995.5616388605245</v>
       </c>
       <c r="E25" s="9">
-        <v>3834.1292538810262</v>
+        <v>4260.611905506752</v>
       </c>
       <c r="F25" s="9">
-        <v>3880.5225423581091</v>
+        <v>4543.2445923979776</v>
       </c>
       <c r="G25" s="9">
-        <v>3927.4771935523045</v>
+        <v>4844.6260499989003</v>
       </c>
       <c r="H25" s="9">
-        <v>3975.0000000000005</v>
+        <v>5165.9999999999991</v>
       </c>
       <c r="I25" s="5">
-        <v>4011.3298242590581</v>
+        <v>5337.6130294412269</v>
       </c>
       <c r="J25" s="5">
-        <v>4047.9916877962783</v>
+        <v>5514.9269942045594</v>
       </c>
       <c r="K25" s="5">
-        <v>4084.9886253106852</v>
+        <v>5698.1312777164921</v>
       </c>
       <c r="L25" s="5">
-        <v>4122.3236992371731</v>
+        <v>5887.4215546663063</v>
       </c>
       <c r="M25" s="5">
-        <v>4160</v>
+        <v>6083.0000000000009</v>
       </c>
       <c r="N25" s="6">
-        <v>4190.548047579573</v>
+        <v>6199.2695146082551</v>
       </c>
       <c r="O25" s="6">
-        <v>4221.3204180463872</v>
+        <v>6317.7613866104339</v>
       </c>
       <c r="P25" s="6">
-        <v>4252.3187586663644</v>
+        <v>6438.5180937996447</v>
       </c>
       <c r="Q25" s="6">
-        <v>4283.5447288017613</v>
+        <v>6561.5829258829181</v>
       </c>
       <c r="R25" s="6">
-        <v>4314.9999999999982</v>
+        <v>6687.0000000000018</v>
       </c>
       <c r="S25" s="7">
-        <v>4340.6922214399192</v>
+        <v>6805.0032975062168</v>
       </c>
       <c r="T25" s="7">
-        <v>4366.5374186023218</v>
+        <v>6925.088960530953</v>
       </c>
       <c r="U25" s="7">
-        <v>4392.5365023298818</v>
+        <v>7047.2937358960717</v>
       </c>
       <c r="V25" s="7">
-        <v>4418.6903888885809</v>
+        <v>7171.6550188825586</v>
       </c>
       <c r="W25" s="7">
-        <v>4444.9999999999982</v>
+        <v>7298.2108646736679</v>
       </c>
       <c r="X25" s="10">
-        <v>4466.7854057624545</v>
-      </c>
-      <c r="Y25" s="10">
-        <v>4488.6775840567971</v>
-      </c>
-      <c r="Z25" s="10">
-        <v>4510.6770581862729</v>
-      </c>
-      <c r="AA25" s="10">
-        <v>4532.7843540188915</v>
-      </c>
-      <c r="AB25" s="10">
-        <v>4554.9999999999973</v>
+        <v>7427.0000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:24">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3088,82 +2788,70 @@
         <v>11723</v>
       </c>
       <c r="D26" s="9">
-        <v>11782.003066108971</v>
+        <v>11650.919027868707</v>
       </c>
       <c r="E26" s="9">
-        <v>11841.303100725174</v>
+        <v>11579.281258547564</v>
       </c>
       <c r="F26" s="9">
-        <v>11900.901598521681</v>
+        <v>11508.083966924449</v>
       </c>
       <c r="G26" s="9">
-        <v>11960.800061694414</v>
+        <v>11437.324444643082</v>
       </c>
       <c r="H26" s="9">
-        <v>12020.999999999996</v>
+        <v>11366.999999999998</v>
       </c>
       <c r="I26" s="5">
-        <v>12049.464874805311</v>
+        <v>11260.212320000132</v>
       </c>
       <c r="J26" s="5">
-        <v>12077.997152413856</v>
+        <v>11154.427860603742</v>
       </c>
       <c r="K26" s="5">
-        <v>12106.59699243069</v>
+        <v>11049.637197019703</v>
       </c>
       <c r="L26" s="5">
-        <v>12135.264554838801</v>
+        <v>10945.830992998413</v>
       </c>
       <c r="M26" s="5">
-        <v>12164.000000000004</v>
+        <v>10843</v>
       </c>
       <c r="N26" s="6">
-        <v>12182.344585381656</v>
+        <v>10811.416542757055</v>
       </c>
       <c r="O26" s="6">
-        <v>12200.716836318459</v>
+        <v>10779.925081711788</v>
       </c>
       <c r="P26" s="6">
-        <v>12219.116794532965</v>
+        <v>10748.525348897954</v>
       </c>
       <c r="Q26" s="6">
-        <v>12237.544501810647</v>
+        <v>10717.217077129842</v>
       </c>
       <c r="R26" s="6">
-        <v>12256</v>
+        <v>10686</v>
       </c>
       <c r="S26" s="7">
-        <v>12269.569917321658</v>
+        <v>10713.160167656879</v>
       </c>
       <c r="T26" s="7">
-        <v>12283.154859337843</v>
+        <v>10740.389367197266</v>
       </c>
       <c r="U26" s="7">
-        <v>12296.754842683988</v>
+        <v>10767.687774076663</v>
       </c>
       <c r="V26" s="7">
-        <v>12310.369884013942</v>
+        <v>10795.055564196526</v>
       </c>
       <c r="W26" s="7">
-        <v>12323.999999999998</v>
+        <v>10822.492913905389</v>
       </c>
       <c r="X26" s="10">
-        <v>12342.544108762315</v>
-      </c>
-      <c r="Y26" s="10">
-        <v>12361.116121124907</v>
-      </c>
-      <c r="Z26" s="10">
-        <v>12379.716079074742</v>
-      </c>
-      <c r="AA26" s="10">
-        <v>12398.344024661967</v>
-      </c>
-      <c r="AB26" s="10">
-        <v>12417.000000000002</v>
+        <v>10850.000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:24">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3174,82 +2862,70 @@
         <v>2985</v>
       </c>
       <c r="D27" s="9">
-        <v>2953.7526085256136</v>
+        <v>3038.6374296152644</v>
       </c>
       <c r="E27" s="9">
-        <v>2922.8323190525521</v>
+        <v>3093.2386695674572</v>
       </c>
       <c r="F27" s="9">
-        <v>2892.2357074319748</v>
+        <v>3148.8210385530979</v>
       </c>
       <c r="G27" s="9">
-        <v>2861.9593853595043</v>
+        <v>3205.4021664681582</v>
       </c>
       <c r="H27" s="9">
-        <v>2831.9999999999995</v>
+        <v>3263.0000000000009</v>
       </c>
       <c r="I27" s="5">
-        <v>2865.0209254351162</v>
+        <v>3358.4499964085276</v>
       </c>
       <c r="J27" s="5">
-        <v>2898.4268725921929</v>
+        <v>3456.6921171855465</v>
       </c>
       <c r="K27" s="5">
-        <v>2932.2223307980562</v>
+        <v>3557.8080381695322</v>
       </c>
       <c r="L27" s="5">
-        <v>2966.4118417247741</v>
+        <v>3661.8818243986198</v>
       </c>
       <c r="M27" s="5">
-        <v>3001</v>
+        <v>3768.9999999999991</v>
       </c>
       <c r="N27" s="6">
-        <v>3038.4533998546813</v>
+        <v>3843.7736650517268</v>
       </c>
       <c r="O27" s="6">
-        <v>3076.3742296196174</v>
+        <v>3920.0307742491864</v>
       </c>
       <c r="P27" s="6">
-        <v>3114.7683229633631</v>
+        <v>3997.8007578273687</v>
       </c>
       <c r="Q27" s="6">
-        <v>3153.6415863604443</v>
+        <v>4077.1136298913971</v>
       </c>
       <c r="R27" s="6">
-        <v>3193.0000000000005</v>
+        <v>4158.0000000000009</v>
       </c>
       <c r="S27" s="7">
-        <v>3228.5973819607125</v>
+        <v>4216.0989437765338</v>
       </c>
       <c r="T27" s="7">
-        <v>3264.5916238031837</v>
+        <v>4275.0096930528143</v>
       </c>
       <c r="U27" s="7">
-        <v>3300.9871499473315</v>
+        <v>4334.7435910328077</v>
       </c>
       <c r="V27" s="7">
-        <v>3337.7884341390254</v>
+        <v>4395.312139416912</v>
       </c>
       <c r="W27" s="7">
-        <v>3375.0000000000009</v>
+        <v>4456.7270006165991</v>
       </c>
       <c r="X27" s="10">
-        <v>3409.2958697260478</v>
-      </c>
-      <c r="Y27" s="10">
-        <v>3443.9402451351366</v>
-      </c>
-      <c r="Z27" s="10">
-        <v>3478.9366676511199</v>
-      </c>
-      <c r="AA27" s="10">
-        <v>3514.288714684877</v>
-      </c>
-      <c r="AB27" s="10">
-        <v>3550.0000000000027</v>
+        <v>4519.0000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:28">
+    <row r="28" spans="1:24">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3260,79 +2936,67 @@
         <v>247</v>
       </c>
       <c r="D28" s="9">
-        <v>247.39871071213736</v>
+        <v>257.13367163651259</v>
       </c>
       <c r="E28" s="9">
-        <v>247.79806502845275</v>
+        <v>267.68309752742459</v>
       </c>
       <c r="F28" s="9">
-        <v>248.19806398786068</v>
+        <v>278.66533482696906</v>
       </c>
       <c r="G28" s="9">
-        <v>248.59870863095264</v>
+        <v>290.09814049342788</v>
       </c>
       <c r="H28" s="9">
-        <v>248.99999999999991</v>
+        <v>301.99999999999989</v>
       </c>
       <c r="I28" s="5">
-        <v>249.39872101827484</v>
+        <v>312.97308786027418</v>
       </c>
       <c r="J28" s="5">
-        <v>249.79808050422204</v>
+        <v>324.34487988342681</v>
       </c>
       <c r="K28" s="5">
-        <v>250.19807948021298</v>
+        <v>336.12986287677421</v>
       </c>
       <c r="L28" s="5">
-        <v>250.59871897025619</v>
+        <v>348.34305002183629</v>
       </c>
       <c r="M28" s="5">
-        <v>250.99999999999994</v>
+        <v>361.00000000000017</v>
       </c>
       <c r="N28" s="6">
-        <v>253.73954220022321</v>
+        <v>367.9288668214005</v>
       </c>
       <c r="O28" s="6">
-        <v>256.50898516326237</v>
+        <v>374.99072310382235</v>
       </c>
       <c r="P28" s="6">
-        <v>259.30865524131491</v>
+        <v>382.18812138539317</v>
       </c>
       <c r="Q28" s="6">
-        <v>262.13888234855284</v>
+        <v>389.5236631964753</v>
       </c>
       <c r="R28" s="6">
-        <v>264.99999999999989</v>
+        <v>397.00000000000006</v>
       </c>
       <c r="S28" s="7">
-        <v>267.93429470017725</v>
+        <v>396.8331581405551</v>
       </c>
       <c r="T28" s="7">
-        <v>270.90108028860914</v>
+        <v>396.66638639749829</v>
       </c>
       <c r="U28" s="7">
-        <v>273.90071653073426</v>
+        <v>396.49968474136267</v>
       </c>
       <c r="V28" s="7">
-        <v>276.9335671756055</v>
+        <v>396.33305314269376</v>
       </c>
       <c r="W28" s="7">
-        <v>280.00000000000006</v>
+        <v>396.16649157204944</v>
       </c>
       <c r="X28" s="10">
-        <v>284.26789506145917</v>
-      </c>
-      <c r="Y28" s="10">
-        <v>288.60084343811695</v>
-      </c>
-      <c r="Z28" s="10">
-        <v>292.99983670398296</v>
-      </c>
-      <c r="AA28" s="10">
-        <v>297.46588154711606</v>
-      </c>
-      <c r="AB28" s="10">
-        <v>302.00000000000006</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/LAS_Lahan.xlsx
+++ b/LAS_Lahan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{D03EF15D-8605-4222-BE4D-E6B1670DA91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3014990D-9085-4025-872E-04915DF563AD}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{D03EF15D-8605-4222-BE4D-E6B1670DA91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86FFF018-76B6-4641-BBD1-01FD2664AD32}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{BEED62CF-6B6B-4A19-9E26-39E82E5ABA88}"/>
   </bookViews>
@@ -923,6 +923,7 @@
   <dimension ref="A1:X28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
